--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488077_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488077_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. PENA BANOS</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.073</v>
+        <v>2.3125</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2328</v>
+        <v>2.078</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1598</v>
+        <v>0.2346</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7211</v>
+        <v>0.47</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9577</v>
+        <v>-1.2633</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7634</v>
+        <v>1.7333</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6119</v>
+        <v>2.9737</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8771</v>
+        <v>-0.2081</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7349</v>
+        <v>3.1818</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8909</v>
+        <v>-2.5037</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9194</v>
+        <v>-1.0552</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0285</v>
+        <v>-1.4485</v>
       </c>
       <c r="P2" t="n">
         <v>-0.1982</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9822</v>
+        <v>-2.1805</v>
       </c>
       <c r="R2" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2241</v>
+        <v>0.5671</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8629</v>
+        <v>-0.1889</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3613</v>
+        <v>0.756</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.674</v>
+        <v>1.4737</v>
       </c>
       <c r="W2" t="n">
-        <v>1.7403</v>
+        <v>1.4737</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. PEÑA BAÑOS</t>
+          <t>N. PENA BANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8107</v>
+        <v>2.0969</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8107</v>
+        <v>2.5656</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.4687</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8107</v>
+        <v>1.7211</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.9577</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2053</v>
+        <v>0.7634</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8107</v>
+        <v>2.6119</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.8771</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2053</v>
+        <v>0.7349</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.8909</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.9194</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.0285</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.248</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.1956</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.0524</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CONTRERAS RUBIÑO</t>
+          <t>N. PEÑA BAÑOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5107</v>
+        <v>1.8107</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5107</v>
+        <v>1.8107</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5107</v>
+        <v>1.8107</v>
       </c>
       <c r="H4" t="n">
-        <v>0.908</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6027</v>
+        <v>1.2053</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5107</v>
+        <v>1.8107</v>
       </c>
       <c r="K4" t="n">
-        <v>0.908</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6027</v>
+        <v>1.2053</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>A. CONTRERAS RUBIÑO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4517</v>
+        <v>1.5107</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2172</v>
+        <v>1.5107</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2346</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.47</v>
+        <v>1.5107</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2633</v>
+        <v>0.908</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7333</v>
+        <v>0.6027</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9737</v>
+        <v>1.5107</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2081</v>
+        <v>0.908</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1818</v>
+        <v>0.6027</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5037</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0552</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4485</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1805</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2937</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0497</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.756</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9099</v>
+        <v>0.8391</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9867</v>
+        <v>-1.7206</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8966</v>
+        <v>2.5597</v>
       </c>
       <c r="G6" t="n">
         <v>0.048</v>
@@ -922,13 +922,13 @@
         <v>1.1893</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3773</v>
+        <v>0.3065</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.301</v>
+        <v>-0.0348</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6782</v>
+        <v>0.3413</v>
       </c>
       <c r="V6" t="n">
         <v>1.2775</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7003</v>
+        <v>0.8189</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0534</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7537</v>
+        <v>0.8099</v>
       </c>
       <c r="G7" t="n">
         <v>0.5271</v>
@@ -1000,13 +1000,13 @@
         <v>0.3964</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2232</v>
+        <v>-0.1046</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4368</v>
+        <v>-0.3744</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2136</v>
+        <v>0.2698</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1228</v>
+        <v>0.3432</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7152</v>
+        <v>1.8795</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5924</v>
+        <v>-1.5362</v>
       </c>
       <c r="G8" t="n">
         <v>0.896</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1608</v>
+        <v>0.0596</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3744</v>
+        <v>-0.2101</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2136</v>
+        <v>0.2698</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2071</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0437</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9516</v>
+        <v>-0.74</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0231</v>
+        <v>0.7837</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6774</v>
+        <v>0.277</v>
       </c>
       <c r="H9" t="n">
-        <v>1.657</v>
+        <v>0.5984</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9796</v>
+        <v>-0.3214</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0464</v>
+        <v>1.5889</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6413</v>
+        <v>1.6615</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5949</v>
+        <v>-0.0726</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.369</v>
+        <v>-1.3119</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0157</v>
+        <v>-1.0631</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3847</v>
+        <v>-0.2488</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3787</v>
+        <v>0.1982</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1627</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1692</v>
+        <v>-0.0945</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2351</v>
+        <v>-0.7322</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9341</v>
+        <v>0.6377</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6036</v>
+        <v>-0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0704</v>
+        <v>-0.4074</v>
       </c>
       <c r="X9" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6499</v>
+        <v>-0.5324</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0686</v>
+        <v>-3.4151</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4187</v>
+        <v>2.8827</v>
       </c>
       <c r="G10" t="n">
-        <v>0.277</v>
+        <v>0.6774</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5984</v>
+        <v>1.657</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3214</v>
+        <v>-0.9796</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5889</v>
+        <v>1.0464</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6615</v>
+        <v>1.6413</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0726</v>
+        <v>-0.5949</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3119</v>
+        <v>-0.369</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0631</v>
+        <v>0.0157</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2488</v>
+        <v>-0.3847</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1982</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1893</v>
+        <v>-4.1627</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7881</v>
+        <v>0.5653</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0608</v>
+        <v>-0.2284</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2727</v>
+        <v>0.7937</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.337</v>
+        <v>0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.4074</v>
+        <v>-0.0704</v>
       </c>
       <c r="X10" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4082</v>
+        <v>-1.2343</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.7232</v>
+        <v>-3.0266</v>
       </c>
       <c r="F11" t="n">
-        <v>1.315</v>
+        <v>1.7924</v>
       </c>
       <c r="G11" t="n">
         <v>1.7314</v>
@@ -1312,13 +1312,13 @@
         <v>1.9822</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8491</v>
+        <v>0.3248</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6753</v>
+        <v>0.0212</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1737</v>
+        <v>0.3036</v>
       </c>
       <c r="V11" t="n">
         <v>0.674</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7203</v>
+        <v>-3.1684</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1095</v>
+        <v>-1.0242</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6108</v>
+        <v>-2.1443</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3401</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3622</v>
+        <v>0.914</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4954</v>
+        <v>-0.4101</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8575</v>
+        <v>1.324</v>
       </c>
       <c r="V12" t="n">
         <v>0.2666</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.7963</v>
+        <v>-5.2046</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3749</v>
+        <v>-4.1482</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4214</v>
+        <v>-1.0563</v>
       </c>
       <c r="G13" t="n">
         <v>-0.5931</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8908</v>
+        <v>-0.2991</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9984</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1075</v>
+        <v>0.4725</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7444</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.924099999999999</v>
+        <v>-0.3639999999999981</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.7813</v>
+        <v>-4.221200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8573</v>
+        <v>3.857499999999998</v>
       </c>
       <c r="G14" t="n">
         <v>3.7362</v>
       </c>
       <c r="H14" t="n">
-        <v>1.727299999999999</v>
+        <v>1.7273</v>
       </c>
       <c r="I14" t="n">
         <v>2.0088</v>
@@ -1531,7 +1531,7 @@
         <v>-10.7716</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.924799999999999</v>
+        <v>-6.9248</v>
       </c>
       <c r="O14" t="n">
         <v>-3.8466</v>
@@ -1546,10 +1546,10 @@
         <v>12.8844</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9271</v>
+        <v>3.4871</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.2938</v>
+        <v>-2.7338</v>
       </c>
       <c r="U14" t="n">
         <v>6.220800000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3984</v>
+        <v>4.9287</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6056</v>
+        <v>4.9112</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2072</v>
+        <v>0.0175</v>
       </c>
       <c r="G15" t="n">
         <v>2.6575</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.3295</v>
+        <v>-0.7993</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9984</v>
+        <v>-0.6927</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3312</v>
+        <v>-0.1065</v>
       </c>
       <c r="V15" t="n">
         <v>1.8811</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ GUZMAN</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7179</v>
+        <v>2.5449</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6816</v>
+        <v>1.4164</v>
       </c>
       <c r="F16" t="n">
-        <v>3.3995</v>
+        <v>1.1285</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2955</v>
+        <v>2.1928</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6004</v>
+        <v>2.0054</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3049</v>
+        <v>0.1874</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5397</v>
+        <v>1.6342</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0581</v>
+        <v>1.594</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5184</v>
+        <v>0.0402</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2442</v>
+        <v>0.5586</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4577</v>
+        <v>0.4114</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.7864</v>
+        <v>0.1472</v>
       </c>
       <c r="P16" t="n">
-        <v>0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3787</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9733</v>
+        <v>0.7929</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6206</v>
+        <v>-0.0533</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0497</v>
+        <v>-0.3634</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6704</v>
+        <v>0.3101</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2071</v>
+        <v>1.1367</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>J. MARTINEZ GUZMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6011</v>
+        <v>2.4221</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4164</v>
+        <v>-0.5797</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1846</v>
+        <v>3.0018</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1928</v>
+        <v>0.2955</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0054</v>
+        <v>1.6004</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1874</v>
+        <v>-1.3049</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6342</v>
+        <v>1.5397</v>
       </c>
       <c r="K17" t="n">
-        <v>1.594</v>
+        <v>2.0581</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>-0.5184</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5586</v>
+        <v>-1.2442</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4114</v>
+        <v>-0.4577</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1472</v>
+        <v>-0.7864</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-2.3787</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7929</v>
+        <v>2.9733</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0029</v>
+        <v>0.3248</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3634</v>
+        <v>-0.9479</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3662</v>
+        <v>1.2727</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1367</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1665</v>
+        <v>0.2271</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2162</v>
+        <v>0.9564</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0496</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0804</v>
+        <v>0.8115</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.0463</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0804</v>
+        <v>1.8578</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0804</v>
+        <v>4.0585</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3505</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0804</v>
+        <v>3.708</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-3.247</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-1.3967</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.8503</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.3609</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1982</v>
+        <v>3.3698</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1545</v>
+        <v>-0.4634</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1358</v>
+        <v>-0.8184</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0187</v>
+        <v>0.355</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2666</v>
+        <v>0.8701</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MORALES MUNOZ</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0144</v>
+        <v>0.1946</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3463</v>
+        <v>0.2162</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3607</v>
+        <v>-0.0216</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7692</v>
+        <v>0.0804</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2834</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4858</v>
+        <v>0.0804</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3406</v>
+        <v>0.0804</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9155</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.4251</v>
+        <v>0.0804</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1098</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1989</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9109</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3876</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9733</v>
+        <v>0.1982</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5356</v>
+        <v>0.1826</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2993</v>
+        <v>0.1358</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7637</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2666</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>J. MORALES MUNOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3443</v>
+        <v>0.1692</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5489000000000001</v>
+        <v>-0.9388</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8932</v>
+        <v>1.108</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8115</v>
+        <v>-0.7692</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0463</v>
+        <v>-0.2834</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8578</v>
+        <v>-0.4858</v>
       </c>
       <c r="J21" t="n">
-        <v>4.0585</v>
+        <v>1.3406</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3505</v>
+        <v>0.9155</v>
       </c>
       <c r="L21" t="n">
-        <v>3.708</v>
+        <v>0.4251</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.247</v>
+        <v>-2.1098</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3967</v>
+        <v>-1.1989</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8503</v>
+        <v>-0.9109</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.3609</v>
+        <v>-1.3876</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3698</v>
+        <v>2.9733</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0348</v>
+        <v>-0.3808</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2259</v>
+        <v>-0.8918</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1911</v>
+        <v>0.511</v>
       </c>
       <c r="V21" t="n">
-        <v>0.8701</v>
+        <v>-0.2666</v>
       </c>
       <c r="W21" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="22">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9828</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="E23" t="n">
         <v>-1.7169</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7342</v>
+        <v>1.043</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5599</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4181</v>
+        <v>-0.1092</v>
       </c>
       <c r="T23" t="n">
         <v>-0.7488</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3307</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3923</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0301</v>
+        <v>-1.309</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1449</v>
+        <v>0.5337</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.175</v>
+        <v>-1.8427</v>
       </c>
       <c r="G24" t="n">
         <v>-0.6773</v>
@@ -2326,13 +2326,13 @@
         <v>1.9822</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2596</v>
+        <v>-0.0192</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5471</v>
+        <v>-0.0641</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2875</v>
+        <v>0.0449</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2071</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8895</v>
+        <v>-2.6176</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.6062</v>
+        <v>-3.2175</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7167</v>
+        <v>0.5998</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0828</v>
@@ -2404,13 +2404,13 @@
         <v>2.3787</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6868</v>
+        <v>-0.0413</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3709</v>
+        <v>-0.2403</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3159</v>
+        <v>0.199</v>
       </c>
       <c r="V25" t="n">
         <v>-0.674</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.9561</v>
+        <v>-3.5114</v>
       </c>
       <c r="E26" t="n">
         <v>-2.9394</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0167</v>
+        <v>-0.572</v>
       </c>
       <c r="G26" t="n">
         <v>-1.1745</v>
@@ -2482,13 +2482,13 @@
         <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.1606</v>
       </c>
       <c r="T26" t="n">
         <v>-0.8001</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1949</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7621</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.923800000000002</v>
+        <v>2.603000000000003</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.857399999999999</v>
+        <v>-3.8574</v>
       </c>
       <c r="F27" t="n">
-        <v>5.781300000000002</v>
+        <v>6.4603</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.736199999999999</v>
+        <v>-3.736199999999998</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.727300000000001</v>
+        <v>-1.7273</v>
       </c>
       <c r="I27" t="n">
         <v>-2.0089</v>
@@ -2560,13 +2560,13 @@
         <v>21.8045</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.9272</v>
+        <v>-1.248</v>
       </c>
       <c r="T27" t="n">
-        <v>-6.2209</v>
+        <v>-6.220800000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>4.293699999999999</v>
+        <v>4.973</v>
       </c>
       <c r="V27" t="n">
         <v>-1.3328</v>
